--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Bohål på låga, har varit 1,5 meter upp,  diameter 4 till 5 cm. Tretåig hackspett?</t>
+          <t>Bohål på låga, har varit 1,5 meter upp,  diameter 4 till 5 cm. Tretåig hackspett</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>137093712</v>
       </c>
       <c r="B23" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>137093718</v>
       </c>
       <c r="B24" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>137093733</v>
       </c>
       <c r="B25" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>137093739</v>
       </c>
       <c r="B26" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>137093715</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>137093716</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>137093721</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>137093723</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>137093727</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137093724</v>
       </c>
       <c r="B32" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>137093712</v>
       </c>
       <c r="B23" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>137093718</v>
       </c>
       <c r="B24" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>137093733</v>
       </c>
       <c r="B25" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>137093739</v>
       </c>
       <c r="B26" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>137093715</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>137093716</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>137093721</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>137093723</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>137093727</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137093724</v>
       </c>
       <c r="B32" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137093719</v>
       </c>
       <c r="B33" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -3080,11 +3080,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fisklösen, Dlr</t>
@@ -3197,11 +3193,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fisklösen, Dlr</t>
@@ -3314,11 +3306,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fisklösen, Dlr</t>
@@ -3543,11 +3531,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fisklösen, Dlr</t>
@@ -3662,11 +3646,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3785,11 +3765,7 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fisklösen, Dlr</t>
@@ -3902,11 +3878,7 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fisklösen, Dlr</t>
@@ -4021,11 +3993,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4144,11 +4112,7 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fisklösen, Dlr</t>
@@ -4261,11 +4225,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fisklösen, Dlr</t>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>137093712</v>
       </c>
       <c r="B23" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137093718</v>
       </c>
       <c r="B24" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>137093733</v>
       </c>
       <c r="B25" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137093739</v>
       </c>
       <c r="B26" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137093715</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>137093716</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>137093721</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>137093723</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>137093727</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137093724</v>
       </c>
       <c r="B32" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>137093719</v>
       </c>
       <c r="B33" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>137093712</v>
       </c>
       <c r="B23" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137093718</v>
       </c>
       <c r="B24" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>137093733</v>
       </c>
       <c r="B25" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137093739</v>
       </c>
       <c r="B26" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137093715</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>137093716</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>137093721</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>137093723</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>137093727</v>
       </c>
       <c r="B31" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137093724</v>
       </c>
       <c r="B32" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>137093712</v>
       </c>
       <c r="B23" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137093718</v>
       </c>
       <c r="B24" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>137093733</v>
       </c>
       <c r="B25" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137093739</v>
       </c>
       <c r="B26" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137093715</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>137093716</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>137093721</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>137093723</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>137093727</v>
       </c>
       <c r="B31" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137093724</v>
       </c>
       <c r="B32" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35234-2026 artfynd.xlsx
+++ b/artfynd/A 35234-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093711</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093731</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093704</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137093705</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137093706</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093707</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137093710</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093713</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093714</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093717</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093722</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137093725</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137093726</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>137093728</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137093730</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137093732</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137093734</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137093736</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137093737</v>
       </c>
       <c r="B20" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>137093741</v>
       </c>
       <c r="B21" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>137093742</v>
       </c>
       <c r="B22" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>137093712</v>
       </c>
       <c r="B23" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137093718</v>
       </c>
       <c r="B24" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>137093733</v>
       </c>
       <c r="B25" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137093739</v>
       </c>
       <c r="B26" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137093715</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>137093716</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>137093721</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>137093723</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>137093727</v>
       </c>
       <c r="B31" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137093724</v>
       </c>
       <c r="B32" t="n">
-        <v>58471</v>
+        <v>58474</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
